--- a/output/(山本)可読性_簡潔性_再構成.xlsx
+++ b/output/(山本)可読性_簡潔性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,14 +461,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>接続詞や関係節による修飾が三重以上に重なる構造を避け、一文における主述の関係および係り受けの距離を最短にして記述している。</t>
+          <t>箇条書きの階層や条件分岐の文章表現において、従属節のネストを原則2階層以内に制限して記述している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】Aサーバーが停止しており、かつBサービスが未起動である場合には、管理者へ通知が送信される設定になっていることが確認される必要がある。(多重の節によって主述の関係が不明瞭である）
-→【適合例】Aサーバー停止かつBサービス未起動の場合、管理者に通知する。</t>
+【非適合例】A機能において、Bシステムと連携する場合で、かつCテーブルのステータスが「完了」であるときに、DフラグがONであれば、E画面に遷移する。（多重の入れ子により条件の全容が把握しにくい。）
+→【適合例】A機能におけるE画面への遷移条件は、以下のすべてを満たす場合とする。
+1.Bシステムと連携する。
+2.Cテーブルのステータスが「完了」である。
+3.DフラグがONである。（箇条書きを用いて論理関係を並列化し、可読性を向上させている。）</t>
         </is>
       </c>
     </row>
@@ -480,13 +483,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>用語定義や設計内容を文書内で唯一の定義(Single Source of Truth)として管理し、他の箇所では定義済みの名称を直接参照する構成を維持している。</t>
+          <t>仕様変更時の修正漏れによる不整合を防ぐため、同一の仕様、要件、または用語の定義を複数の章節で重複して記述せず、共通定義への参照を用いて一元管理している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】「利用者ID」と「ユーザーアカウント名」が同じ情報の定義として別々の章に記述されている。(同一の内容が異なる名称で重複して記述されている）
-→【適合例】「利用者ID」として定義を一箇所に集約し、他箇所ではその用語を参照する。</t>
+          <t>★新規追加
+【非適合例】顧客管理機能仕様書に「消費税算出処理」、受注管理機能仕様書に「税額計算モジュール」として、同一の税率計算ロジックを個別に記述している。（同一仕様の重複定義により、税率変更時の修正漏れリスクが生じる。）
+→【適合例】税率計算ロジックを共通仕様書に定義し、顧客管理機能仕様書および受注管理機能仕様書からは、当該の共通定義を参照する形式で記述している。（共通仕様への参照を用いて一元管理することで、保守性と文書間の一貫性を確保している。）</t>
         </is>
       </c>
     </row>
@@ -498,16 +502,18 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ソースコードにおいて同一定義の多重読み込みを防ぐため、インクルードガード(ifndef)や#pragma once等の重複防止策が全ヘッダファイルに適用されている。</t>
+          <t>（プログラミングにおける参考基準）ソースコードの実装において、モジュールやヘッダファイルの二重読み込みによる定義の衝突を防ぐため、プリプロセッサ命令を用いて読み込み回数を1回に制限している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】ヘッダファイルの読み込み制限がなく、同一のソース内で複数回展開される構成になっている。(二重定義によるエラーの原因となる）
-→【適合例】#ifndef _HEADFILE1_
-#define _HEADFILE1_
-// マクロ定義やグローバル変数のextern宣言などをする
+【非適合例】インクルードガードを記述せずに、ヘッダファイルを定義している。（同一プロジェクト内で複数回読み込まれた場合、コンパイル時に再定義エラーが発生する。）
+→【適合例】インクルードガードを用いて、ヘッダファイルの読み込みを1回に制限している。
+（記述例）
+#ifndef_HEADFILE1_
+#define_HEADFILE1_
+//マクロ定義やグローバル変数のextern宣言などを記述する。
 #endif</t>
         </is>
       </c>
@@ -520,13 +526,13 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>「〜しないわけではない」等の否定を二回繰り返す表現を排除し、条件分岐の論理を肯定形または単純否定を用いて簡潔に記述している。</t>
+          <t>システムの挙動、状態、および制約条件を記述する際、読み手による論理的な解釈の齟齬を防ぐため、「〜しない場合は〜しない」などの二重否定を避け、肯定形を用いて直接的に動作を定義している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】条件に合致しないものはチェックしない。(二重否定により判定条件の解釈に負荷がかかる）
-→【適合例】条件に合致するものだけをチェックする。</t>
+          <t>【非適合例】［例文1］入力値がエラー条件に合致しない場合は、エラー処理を実行しない。（二重否定により、実行条件が直感的に伝わりにくい。）
+→【適合例】［例文1a］入力値がエラー条件に合致する場合のみ、エラー処理を実行する。（肯定形を用いることで、システムが動作する条件を直接的に明確化している。）</t>
         </is>
       </c>
     </row>
@@ -538,32 +544,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>文脈から自明な「〜を行う」「〜といった」等の冗長な助動詞や、技術的判断に寄与しない抽象的な修飾語をすべて削除し、事実を直接的に記述している。</t>
+          <t>システム仕様の理解に寄与しない主観的な形容詞や、実装に関与しない開発の背景事情を排除し、システムが満たすべき機能要件および制約条件のみを客観的な事実として記述している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】データの削除処理を行うにあたっては、確認ダイアログの表示を実行するようにしてください。(「〜を行う」「〜するようにしてください」が冗長である）
-→【適合例】データ削除時は、確認ダイアログを表示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>不要な表記および表現がない</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>当該文書の対象読者にとって既知である一般的な背景説明や、実装に不要な主観的評価を排除し、仕様や数値などの客観的事実のみを記述している。</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>【非適合例】本システムは最新のWeb技術を用いており、非常に高度なセキュリティを確保するために、多層防御の考え方に基づき、不要なポートを閉じる設定を各サーバーに施している。(具体的な設定値に対し、抽象的で不要な背景説明が含まれている）
-→【適合例】多層防御に基づき、各サーバーの不要なポートを閉鎖する。</t>
+【非適合例】ユーザーの利便性を飛躍的に高めるため、本システムは自動的に外部連携を実行し、最新の顧客データを取得する。（機能要件に不要な主観的修飾語が含まれており、仕様の検証可能性を低下させている。）
+→【適合例】本システムは外部APIと連携し、顧客データを自動取得する。（主観的な表現を完全に排除し、システムが実行する客観的な動作要件のみを記述している。）</t>
         </is>
       </c>
     </row>
